--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="191">
   <si>
     <t>!Enum</t>
   </si>
@@ -604,6 +604,10 @@
   </si>
   <si>
     <t>Icon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Stat</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1175,7 +1179,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1373,7 +1377,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>31</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -1179,7 +1179,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -1179,7 +1179,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1451,7 +1451,7 @@
         <v>0.1</v>
       </c>
       <c r="H5" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5" s="8" t="b">
         <v>1</v>
@@ -1799,6 +1799,9 @@
       </c>
       <c r="F21" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="H21" s="1">
+        <v>3</v>
       </c>
       <c r="I21" s="8" t="b">
         <v>1</v>
